--- a/ExpertAdvisors/files/Tabel_Grid.xlsx
+++ b/ExpertAdvisors/files/Tabel_Grid.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -49,7 +49,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="[$$-409]#,##0.00;[RED]\-[$$-409]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$$-3809]#,##0.00;[RED]\-[$$-3809]#,##0.00"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -74,12 +74,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -116,7 +122,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -125,7 +131,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -133,7 +139,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -161,37 +171,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -264,14 +274,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M201"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AA201"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -296,6 +306,21 @@
         <v>4</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="W1" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="X1" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y1" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z1" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA1" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -303,7 +328,7 @@
       <c r="A2" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
@@ -334,13 +359,41 @@
       <c r="K2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="4"/>
+      <c r="L2" s="3"/>
       <c r="M2" s="1" t="n">
         <v>0.01</v>
       </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="V2" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="W2" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="X2" s="4" t="n">
+        <f aca="false">SUM($W2:W2)+($V2-$V$18)</f>
+        <v>30.6</v>
+      </c>
+      <c r="Y2" s="4" t="n">
+        <f aca="false">SUM($W2:X2)+($V2-$V$18)</f>
+        <v>61.2</v>
+      </c>
+      <c r="Z2" s="4" t="n">
+        <f aca="false">SUM($W2:Y2)+($V2-$V$18)</f>
+        <v>122.4</v>
+      </c>
+      <c r="AA2" s="4" t="n">
+        <f aca="false">SUM($W2:Z2)+($V2-$V$21)</f>
+        <v>246.6</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="n">
@@ -373,13 +426,41 @@
         <f aca="false">K2 + (SUM(H$2:H2) * (J3-J2) * 100)</f>
         <v>-0.8</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="3"/>
       <c r="M3" s="1" t="n">
         <v>0.01</v>
       </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="V3" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="W3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X3" s="4" t="n">
+        <f aca="false">SUM($W3:W3)+($V3-$V$18)</f>
+        <v>28.6</v>
+      </c>
+      <c r="Y3" s="4" t="n">
+        <f aca="false">SUM($W3:X3)+($V3-$V$18)</f>
+        <v>57.2</v>
+      </c>
+      <c r="Z3" s="4" t="n">
+        <f aca="false">SUM($W3:Y3)+($V3-$V$18)</f>
+        <v>114.4</v>
+      </c>
+      <c r="AA3" s="4" t="n">
+        <f aca="false">SUM($W3:Z3)+($V3-$V$21)</f>
+        <v>230.6</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="n">
@@ -412,13 +493,41 @@
         <f aca="false">K3 + (SUM(H$2:H3) * (J4-J3) * 100)</f>
         <v>-2.4</v>
       </c>
-      <c r="L4" s="4"/>
+      <c r="L4" s="3"/>
       <c r="M4" s="1" t="n">
         <v>0.01</v>
       </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="V4" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="W4" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="X4" s="4" t="n">
+        <f aca="false">SUM($W4:W4)+($V4-$V$18)</f>
+        <v>26.6</v>
+      </c>
+      <c r="Y4" s="4" t="n">
+        <f aca="false">SUM($W4:X4)+($V4-$V$18)</f>
+        <v>53.2</v>
+      </c>
+      <c r="Z4" s="4" t="n">
+        <f aca="false">SUM($W4:Y4)+($V4-$V$18)</f>
+        <v>106.4</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <f aca="false">SUM($W4:Z4)+($V4-$V$21)</f>
+        <v>214.6</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="1" t="n">
@@ -451,13 +560,41 @@
         <f aca="false">K4 + (SUM(H$2:H4) * (J5-J4) * 100)</f>
         <v>-4.8</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="3"/>
       <c r="M5" s="1" t="n">
         <v>0.01</v>
       </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="V5" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="X5" s="4" t="n">
+        <f aca="false">SUM($W5:W5)+($V5-$V$18)</f>
+        <v>24.6</v>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <f aca="false">SUM($W5:X5)+($V5-$V$18)</f>
+        <v>49.2</v>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <f aca="false">SUM($W5:Y5)+($V5-$V$18)</f>
+        <v>98.4</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <f aca="false">SUM($W5:Z5)+($V5-$V$21)</f>
+        <v>198.6</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="C6" s="1" t="n">
@@ -490,13 +627,41 @@
         <f aca="false">K5 + (SUM(H$2:H5) * (J6-J5) * 100)</f>
         <v>-8</v>
       </c>
-      <c r="L6" s="4"/>
+      <c r="L6" s="3"/>
       <c r="M6" s="1" t="n">
         <v>0.01</v>
       </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="V6" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="W6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X6" s="4" t="n">
+        <f aca="false">SUM($W6:W6)+($V6-$V$18)</f>
+        <v>22.6</v>
+      </c>
+      <c r="Y6" s="4" t="n">
+        <f aca="false">SUM($W6:X6)+($V6-$V$18)</f>
+        <v>45.2</v>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <f aca="false">SUM($W6:Y6)+($V6-$V$18)</f>
+        <v>90.4</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <f aca="false">SUM($W6:Z6)+($V6-$V$21)</f>
+        <v>182.6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="C7" s="1" t="n">
@@ -529,13 +694,40 @@
         <f aca="false">K6 + (SUM(H$2:H6) * (J7-J6) * 100)</f>
         <v>-12</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="3"/>
       <c r="M7" s="1" t="n">
         <v>0.02</v>
       </c>
+      <c r="P7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="3"/>
+      <c r="V7" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X7" s="4" t="n">
+        <f aca="false">SUM($W7:W7)+($V7-$V$18)</f>
+        <v>20.6</v>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <f aca="false">SUM($W7:X7)+($V7-$V$18)</f>
+        <v>41.2</v>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <f aca="false">SUM($W7:Y7)+($V7-$V$18)</f>
+        <v>82.4</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <f aca="false">SUM($W7:Z7)+($V7-$V$21)</f>
+        <v>166.6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="n">
@@ -568,13 +760,40 @@
         <f aca="false">K7 + (SUM(H$2:H7) * (J8-J7) * 100)</f>
         <v>-17.6</v>
       </c>
-      <c r="L8" s="4"/>
+      <c r="L8" s="3"/>
       <c r="M8" s="1" t="n">
         <v>0.02</v>
       </c>
+      <c r="P8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="3"/>
+      <c r="V8" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" s="4" t="n">
+        <f aca="false">SUM($W8:W8)+($V8-$V$18)</f>
+        <v>18.6</v>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <f aca="false">SUM($W8:X8)+($V8-$V$18)</f>
+        <v>37.2</v>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <f aca="false">SUM($W8:Y8)+($V8-$V$18)</f>
+        <v>74.4</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <f aca="false">SUM($W8:Z8)+($V8-$V$21)</f>
+        <v>150.6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="n">
@@ -607,13 +826,40 @@
         <f aca="false">K8 + (SUM(H$2:H8) * (J9-J8) * 100)</f>
         <v>-24.8</v>
       </c>
-      <c r="L9" s="4"/>
+      <c r="L9" s="3"/>
       <c r="M9" s="1" t="n">
         <v>0.02</v>
       </c>
+      <c r="P9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="3"/>
+      <c r="V9" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" s="4" t="n">
+        <f aca="false">SUM($W9:W9)+($V9-$V$18)</f>
+        <v>16.6</v>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <f aca="false">SUM($W9:X9)+($V9-$V$18)</f>
+        <v>33.2</v>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <f aca="false">SUM($W9:Y9)+($V9-$V$18)</f>
+        <v>66.4</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <f aca="false">SUM($W9:Z9)+($V9-$V$21)</f>
+        <v>134.6</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="C10" s="1" t="n">
@@ -646,13 +892,40 @@
         <f aca="false">K9 + (SUM(H$2:H9) * (J10-J9) * 100)</f>
         <v>-33.6</v>
       </c>
-      <c r="L10" s="4"/>
+      <c r="L10" s="3"/>
       <c r="M10" s="1" t="n">
         <v>0.02</v>
       </c>
+      <c r="P10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="3"/>
+      <c r="V10" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="W10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="4" t="n">
+        <f aca="false">SUM($W10:W10)+($V10-$V$18)</f>
+        <v>14.6</v>
+      </c>
+      <c r="Y10" s="4" t="n">
+        <f aca="false">SUM($W10:X10)+($V10-$V$18)</f>
+        <v>29.2</v>
+      </c>
+      <c r="Z10" s="4" t="n">
+        <f aca="false">SUM($W10:Y10)+($V10-$V$18)</f>
+        <v>58.4</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <f aca="false">SUM($W10:Z10)+($V10-$V$21)</f>
+        <v>118.6</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="C11" s="1" t="n">
@@ -685,13 +958,40 @@
         <f aca="false">K10 + (SUM(H$2:H10) * (J11-J10) * 100)</f>
         <v>-44</v>
       </c>
-      <c r="L11" s="4"/>
+      <c r="L11" s="3"/>
       <c r="M11" s="1" t="n">
         <v>0.02</v>
       </c>
+      <c r="P11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="3"/>
+      <c r="V11" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" s="4" t="n">
+        <f aca="false">SUM($W11:W11)+($V11-$V$18)</f>
+        <v>12.6</v>
+      </c>
+      <c r="Y11" s="4" t="n">
+        <f aca="false">SUM($W11:X11)+($V11-$V$18)</f>
+        <v>25.2</v>
+      </c>
+      <c r="Z11" s="4" t="n">
+        <f aca="false">SUM($W11:Y11)+($V11-$V$18)</f>
+        <v>50.4</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <f aca="false">SUM($W11:Z11)+($V11-$V$21)</f>
+        <v>102.6</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="C12" s="1" t="n">
@@ -724,13 +1024,40 @@
         <f aca="false">K11 + (SUM(H$2:H11) * (J12-J11) * 100)</f>
         <v>-56</v>
       </c>
-      <c r="L12" s="4"/>
+      <c r="L12" s="3"/>
       <c r="M12" s="1" t="n">
         <v>0.03</v>
       </c>
+      <c r="P12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="3"/>
+      <c r="V12" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="W12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X12" s="4" t="n">
+        <f aca="false">SUM($W12:W12)+($V12-$V$18)</f>
+        <v>10.6</v>
+      </c>
+      <c r="Y12" s="4" t="n">
+        <f aca="false">SUM($W12:X12)+($V12-$V$18)</f>
+        <v>21.2</v>
+      </c>
+      <c r="Z12" s="4" t="n">
+        <f aca="false">SUM($W12:Y12)+($V12-$V$18)</f>
+        <v>42.4</v>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <f aca="false">SUM($W12:Z12)+($V12-$V$21)</f>
+        <v>86.5999999999999</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="n">
@@ -763,13 +1090,40 @@
         <f aca="false">K12 + (SUM(H$2:H12) * (J13-J12) * 100)</f>
         <v>-70.4</v>
       </c>
-      <c r="L13" s="4"/>
+      <c r="L13" s="3"/>
       <c r="M13" s="1" t="n">
         <v>0.03</v>
       </c>
+      <c r="P13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="3"/>
+      <c r="V13" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="W13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="4" t="n">
+        <f aca="false">SUM($W13:W13)+($V13-$V$18)</f>
+        <v>8.59999999999999</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <f aca="false">SUM($W13:X13)+($V13-$V$18)</f>
+        <v>17.2</v>
+      </c>
+      <c r="Z13" s="4" t="n">
+        <f aca="false">SUM($W13:Y13)+($V13-$V$18)</f>
+        <v>34.4</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <f aca="false">SUM($W13:Z13)+($V13-$V$21)</f>
+        <v>70.5999999999999</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="n">
@@ -802,13 +1156,40 @@
         <f aca="false">K13 + (SUM(H$2:H13) * (J14-J13) * 100)</f>
         <v>-87.2</v>
       </c>
-      <c r="L14" s="4"/>
+      <c r="L14" s="3"/>
       <c r="M14" s="1" t="n">
         <v>0.03</v>
       </c>
+      <c r="P14" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="3"/>
+      <c r="V14" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="W14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" s="4" t="n">
+        <f aca="false">SUM($W14:W14)+($V14-$V$18)</f>
+        <v>6.59999999999999</v>
+      </c>
+      <c r="Y14" s="4" t="n">
+        <f aca="false">SUM($W14:X14)+($V14-$V$18)</f>
+        <v>13.2</v>
+      </c>
+      <c r="Z14" s="4" t="n">
+        <f aca="false">SUM($W14:Y14)+($V14-$V$18)</f>
+        <v>26.4</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <f aca="false">SUM($W14:Z14)+($V14-$V$21)</f>
+        <v>54.5999999999999</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="C15" s="1" t="n">
@@ -841,13 +1222,40 @@
         <f aca="false">K14 + (SUM(H$2:H14) * (J15-J14) * 100)</f>
         <v>-106.4</v>
       </c>
-      <c r="L15" s="4"/>
+      <c r="L15" s="3"/>
       <c r="M15" s="1" t="n">
         <v>0.04</v>
       </c>
+      <c r="P15" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="3"/>
+      <c r="V15" s="4" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <f aca="false">SUM($W15:W15)+($V15-$V$18)</f>
+        <v>3.59999999999999</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <f aca="false">SUM($W15:X15)+($V15-$V$18)</f>
+        <v>7.19999999999999</v>
+      </c>
+      <c r="Z15" s="4" t="n">
+        <f aca="false">SUM($W15:Y15)+($V15-$V$18)</f>
+        <v>14.4</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <f aca="false">SUM($W15:Z15)+($V15-$V$21)</f>
+        <v>30.5999999999999</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="1" t="n">
@@ -880,13 +1288,40 @@
         <f aca="false">K15 + (SUM(H$2:H15) * (J16-J15) * 100)</f>
         <v>-128.8</v>
       </c>
-      <c r="L16" s="4"/>
+      <c r="L16" s="3"/>
       <c r="M16" s="1" t="n">
         <v>0.04</v>
       </c>
+      <c r="P16" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="3"/>
+      <c r="V16" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="W16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" s="6" t="n">
+        <f aca="false">SUM($W16:W16)+($V16-$V$18)</f>
+        <v>2.59999999999999</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <f aca="false">SUM($W16:X16)+($V16-$V$19)</f>
+        <v>5.79999999999998</v>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <f aca="false">SUM($W16:Y16)+($V16-$V$18)</f>
+        <v>11</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <f aca="false">SUM($W16:Z16)+($V16-$V$21)</f>
+        <v>23.7999999999999</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="1" t="n">
@@ -919,13 +1354,37 @@
         <f aca="false">K16 + (SUM(H$2:H16) * (J17-J16) * 100)</f>
         <v>-154.4</v>
       </c>
-      <c r="L17" s="4"/>
+      <c r="L17" s="3"/>
       <c r="M17" s="1" t="n">
         <v>0.05</v>
       </c>
+      <c r="P17" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <f aca="false">0.01*_xlfn.CEILING.MATH(Q17/5)</f>
+        <v>0.01</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <f aca="false">R17*1000+50</f>
+        <v>60</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <f aca="false">-(SUM(S$2:S17)-S$2)/100</f>
+        <v>-0.6</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="C18" s="1" t="n">
@@ -958,13 +1417,36 @@
         <f aca="false">K17 + (SUM(H$2:H17) * (J18-J17) * 100)</f>
         <v>-184</v>
       </c>
-      <c r="L18" s="4"/>
+      <c r="L18" s="3"/>
       <c r="M18" s="1" t="n">
         <v>0.05</v>
       </c>
+      <c r="Q18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <f aca="false">0.01*_xlfn.CEILING.MATH(Q18/5)</f>
+        <v>0.01</v>
+      </c>
+      <c r="S18" s="1" t="n">
+        <f aca="false">R18*1000+50</f>
+        <v>60</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <f aca="false">-(SUM(S$2:S18)-S$2)/100</f>
+        <v>-1.2</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <f aca="false">U17 + (SUM(R$2:R17) * (T18-T17) * 100)</f>
+        <v>-0.6</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <f aca="false">V17-S18/100</f>
+        <v>99.4</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="C19" s="1" t="n">
@@ -997,13 +1479,36 @@
         <f aca="false">K18 + (SUM(H$2:H18) * (J19-J18) * 100)</f>
         <v>-217.6</v>
       </c>
-      <c r="L19" s="4"/>
+      <c r="L19" s="3"/>
       <c r="M19" s="1" t="n">
         <v>0.06</v>
       </c>
+      <c r="Q19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" s="1" t="n">
+        <f aca="false">0.01*_xlfn.CEILING.MATH(Q19/5)</f>
+        <v>0.01</v>
+      </c>
+      <c r="S19" s="1" t="n">
+        <f aca="false">R19*1000+50</f>
+        <v>60</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <f aca="false">-(SUM(S$2:S19)-S$2)/100</f>
+        <v>-1.8</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <f aca="false">U18 + (SUM(R$2:R18) * (T19-T18) * 100)</f>
+        <v>-1.8</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <f aca="false">V18-S19/100</f>
+        <v>98.8</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="C20" s="1" t="n">
@@ -1036,13 +1541,36 @@
         <f aca="false">K19 + (SUM(H$2:H19) * (J20-J19) * 100)</f>
         <v>-256</v>
       </c>
-      <c r="L20" s="4"/>
+      <c r="L20" s="3"/>
       <c r="M20" s="1" t="n">
         <v>0.06</v>
       </c>
+      <c r="Q20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <f aca="false">0.01*_xlfn.CEILING.MATH(Q20/5)</f>
+        <v>0.01</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <f aca="false">R20*1000+50</f>
+        <v>60</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <f aca="false">-(SUM(S$2:S20)-S$2)/100</f>
+        <v>-2.4</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <f aca="false">U19 + (SUM(R$2:R19) * (T20-T19) * 100)</f>
+        <v>-3.6</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <f aca="false">V19-S20/100</f>
+        <v>98.2</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="1" t="n">
@@ -1075,13 +1603,36 @@
         <f aca="false">K20 + (SUM(H$2:H20) * (J21-J20) * 100)</f>
         <v>-299.2</v>
       </c>
-      <c r="L21" s="4"/>
+      <c r="L21" s="3"/>
       <c r="M21" s="1" t="n">
         <v>0.06</v>
       </c>
+      <c r="Q21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R21" s="1" t="n">
+        <f aca="false">0.01*_xlfn.CEILING.MATH(Q21/5)</f>
+        <v>0.01</v>
+      </c>
+      <c r="S21" s="1" t="n">
+        <f aca="false">R21*1000+50</f>
+        <v>60</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <f aca="false">-(SUM(S$2:S21)-S$2)/100</f>
+        <v>-3</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <f aca="false">U20 + (SUM(R$2:R20) * (T21-T20) * 100)</f>
+        <v>-6</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <f aca="false">V20-S21/100</f>
+        <v>97.6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="C22" s="1" t="n">
@@ -1114,13 +1665,22 @@
         <f aca="false">K21 + (SUM(H$2:H21) * (J22-J21) * 100)</f>
         <v>-347.2</v>
       </c>
-      <c r="L22" s="4"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="1" t="n">
         <v>0.06</v>
       </c>
+      <c r="W22" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X22" s="0" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y22" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="C23" s="1" t="n">
@@ -1153,13 +1713,13 @@
         <f aca="false">K22 + (SUM(H$2:H22) * (J23-J22) * 100)</f>
         <v>-400</v>
       </c>
-      <c r="L23" s="4"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="1" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="C24" s="1" t="n">
@@ -1192,13 +1752,13 @@
         <f aca="false">K23 + (SUM(H$2:H23) * (J24-J23) * 100)</f>
         <v>-459.2</v>
       </c>
-      <c r="L24" s="4"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="1" t="n">
         <v>0.08</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="C25" s="1" t="n">
@@ -1231,13 +1791,13 @@
         <f aca="false">K24 + (SUM(H$2:H24) * (J25-J24) * 100)</f>
         <v>-524.8</v>
       </c>
-      <c r="L25" s="4"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="C26" s="1" t="n">
@@ -1270,13 +1830,13 @@
         <f aca="false">K25 + (SUM(H$2:H25) * (J26-J25) * 100)</f>
         <v>-597.6</v>
       </c>
-      <c r="L26" s="4"/>
+      <c r="L26" s="3"/>
       <c r="M26" s="1" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="C27" s="1" t="n">
@@ -1309,13 +1869,13 @@
         <f aca="false">K26 + (SUM(H$2:H26) * (J27-J26) * 100)</f>
         <v>-677.6</v>
       </c>
-      <c r="L27" s="4"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="C28" s="1" t="n">
@@ -1348,13 +1908,13 @@
         <f aca="false">K27 + (SUM(H$2:H27) * (J28-J27) * 100)</f>
         <v>-765.6</v>
       </c>
-      <c r="L28" s="4"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="C29" s="1" t="n">
@@ -1387,13 +1947,13 @@
         <f aca="false">K28 + (SUM(H$2:H28) * (J29-J28) * 100)</f>
         <v>-861.6</v>
       </c>
-      <c r="L29" s="4"/>
+      <c r="L29" s="3"/>
       <c r="M29" s="1" t="n">
         <v>0.11</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="C30" s="1" t="n">
@@ -1426,13 +1986,13 @@
         <f aca="false">K29 + (SUM(H$2:H29) * (J30-J29) * 100)</f>
         <v>-966.4</v>
       </c>
-      <c r="L30" s="4"/>
+      <c r="L30" s="3"/>
       <c r="M30" s="1" t="n">
         <v>0.11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="C31" s="1" t="n">
@@ -1465,13 +2025,13 @@
         <f aca="false">K30 + (SUM(H$2:H30) * (J31-J30) * 100)</f>
         <v>-1080</v>
       </c>
-      <c r="L31" s="4"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="1" t="n">
         <v>0.12</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="C32" s="1" t="n">
@@ -1504,13 +2064,13 @@
         <f aca="false">K31 + (SUM(H$2:H31) * (J32-J31) * 100)</f>
         <v>-1203.2</v>
       </c>
-      <c r="L32" s="4"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="1" t="n">
         <v>0.12</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="C33" s="1" t="n">
@@ -1543,13 +2103,13 @@
         <f aca="false">K32 + (SUM(H$2:H32) * (J33-J32) * 100)</f>
         <v>-1336</v>
       </c>
-      <c r="L33" s="4"/>
+      <c r="L33" s="3"/>
       <c r="M33" s="1" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="C34" s="1" t="n">
@@ -1582,13 +2142,13 @@
         <f aca="false">K33 + (SUM(H$2:H33) * (J34-J33) * 100)</f>
         <v>-1479.2</v>
       </c>
-      <c r="L34" s="4"/>
+      <c r="L34" s="3"/>
       <c r="M34" s="1" t="n">
         <v>0.13</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="C35" s="1" t="n">
@@ -1621,13 +2181,13 @@
         <f aca="false">K34 + (SUM(H$2:H34) * (J35-J34) * 100)</f>
         <v>-1632.8</v>
       </c>
-      <c r="L35" s="4"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="1" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="C36" s="1" t="n">
@@ -1660,13 +2220,13 @@
         <f aca="false">K35 + (SUM(H$2:H35) * (J36-J35) * 100)</f>
         <v>-1797.6</v>
       </c>
-      <c r="L36" s="4"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="1" t="n">
         <v>0.14</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="C37" s="1" t="n">
@@ -1699,13 +2259,13 @@
         <f aca="false">K36 + (SUM(H$2:H36) * (J37-J36) * 100)</f>
         <v>-1973.6</v>
       </c>
-      <c r="L37" s="4"/>
+      <c r="L37" s="3"/>
       <c r="M37" s="1" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="C38" s="1" t="n">
@@ -1738,13 +2298,13 @@
         <f aca="false">K37 + (SUM(H$2:H37) * (J38-J37) * 100)</f>
         <v>-2161.6</v>
       </c>
-      <c r="L38" s="4"/>
+      <c r="L38" s="3"/>
       <c r="M38" s="1" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="C39" s="1" t="n">
@@ -1777,13 +2337,13 @@
         <f aca="false">K38 + (SUM(H$2:H38) * (J39-J38) * 100)</f>
         <v>-2361.6</v>
       </c>
-      <c r="L39" s="4"/>
+      <c r="L39" s="3"/>
       <c r="M39" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0" t="n">
+      <c r="B40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="C40" s="1" t="n">
@@ -1816,13 +2376,13 @@
         <f aca="false">K39 + (SUM(H$2:H39) * (J40-J39) * 100)</f>
         <v>-2574.4</v>
       </c>
-      <c r="L40" s="4"/>
+      <c r="L40" s="3"/>
       <c r="M40" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="n">
+      <c r="B41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="C41" s="1" t="n">
@@ -1855,13 +2415,13 @@
         <f aca="false">K40 + (SUM(H$2:H40) * (J41-J40) * 100)</f>
         <v>-2800</v>
       </c>
-      <c r="L41" s="4"/>
+      <c r="L41" s="3"/>
       <c r="M41" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="n">
+      <c r="B42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="C42" s="1" t="n">
@@ -1894,13 +2454,13 @@
         <f aca="false">K41 + (SUM(H$2:H41) * (J42-J41) * 100)</f>
         <v>-3038.4</v>
       </c>
-      <c r="L42" s="4"/>
+      <c r="L42" s="3"/>
       <c r="M42" s="1" t="n">
         <v>0.16</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="0" t="n">
+      <c r="B43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="C43" s="1" t="n">
@@ -1933,13 +2493,13 @@
         <f aca="false">K42 + (SUM(H$2:H42) * (J43-J42) * 100)</f>
         <v>-3289.6</v>
       </c>
-      <c r="L43" s="4"/>
+      <c r="L43" s="3"/>
       <c r="M43" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="0" t="n">
+      <c r="B44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="C44" s="1" t="n">
@@ -1972,13 +2532,13 @@
         <f aca="false">K43 + (SUM(H$2:H43) * (J44-J43) * 100)</f>
         <v>-3555.2</v>
       </c>
-      <c r="L44" s="4"/>
+      <c r="L44" s="3"/>
       <c r="M44" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="n">
+      <c r="B45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="1" t="n">
@@ -2011,13 +2571,13 @@
         <f aca="false">K44 + (SUM(H$2:H44) * (J45-J44) * 100)</f>
         <v>-3835.2</v>
       </c>
-      <c r="L45" s="4"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="1" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="n">
+      <c r="B46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="C46" s="1" t="n">
@@ -2050,13 +2610,13 @@
         <f aca="false">K45 + (SUM(H$2:H45) * (J46-J45) * 100)</f>
         <v>-4130.4</v>
       </c>
-      <c r="L46" s="4"/>
+      <c r="L46" s="3"/>
       <c r="M46" s="1" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="0" t="n">
+      <c r="B47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="C47" s="1" t="n">
@@ -2089,13 +2649,13 @@
         <f aca="false">K46 + (SUM(H$2:H46) * (J47-J46) * 100)</f>
         <v>-4440.8</v>
       </c>
-      <c r="L47" s="4"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="0" t="n">
+      <c r="B48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="C48" s="1" t="n">
@@ -2128,13 +2688,13 @@
         <f aca="false">K47 + (SUM(H$2:H47) * (J48-J47) * 100)</f>
         <v>-4767.2</v>
       </c>
-      <c r="L48" s="4"/>
+      <c r="L48" s="3"/>
       <c r="M48" s="1" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="0" t="n">
+      <c r="B49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="C49" s="1" t="n">
@@ -2167,13 +2727,13 @@
         <f aca="false">K48 + (SUM(H$2:H48) * (J49-J48) * 100)</f>
         <v>-5109.6</v>
       </c>
-      <c r="L49" s="4"/>
+      <c r="L49" s="3"/>
       <c r="M49" s="1" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="0" t="n">
+      <c r="B50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="C50" s="1" t="n">
@@ -2206,13 +2766,13 @@
         <f aca="false">K49 + (SUM(H$2:H49) * (J50-J49) * 100)</f>
         <v>-5468.8</v>
       </c>
-      <c r="L50" s="4"/>
+      <c r="L50" s="3"/>
       <c r="M50" s="1" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="0" t="n">
+      <c r="B51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="C51" s="1" t="n">
@@ -2245,13 +2805,13 @@
         <f aca="false">K50 + (SUM(H$2:H50) * (J51-J50) * 100)</f>
         <v>-5844.8</v>
       </c>
-      <c r="L51" s="4"/>
+      <c r="L51" s="3"/>
       <c r="M51" s="1" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="0" t="n">
+      <c r="B52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="C52" s="1" t="n">
@@ -2284,13 +2844,13 @@
         <f aca="false">K51 + (SUM(H$2:H51) * (J52-J51) * 100)</f>
         <v>-6238.4</v>
       </c>
-      <c r="L52" s="4"/>
+      <c r="L52" s="3"/>
       <c r="M52" s="1" t="n">
         <v>0.22</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="0" t="n">
+      <c r="B53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="C53" s="1" t="n">
@@ -2323,13 +2883,13 @@
         <f aca="false">K52 + (SUM(H$2:H52) * (J53-J52) * 100)</f>
         <v>-6649.6</v>
       </c>
-      <c r="L53" s="4"/>
+      <c r="L53" s="3"/>
       <c r="M53" s="1" t="n">
         <v>0.23</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="0" t="n">
+      <c r="B54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="C54" s="1" t="n">
@@ -2362,13 +2922,13 @@
         <f aca="false">K53 + (SUM(H$2:H53) * (J54-J53) * 100)</f>
         <v>-7079.2</v>
       </c>
-      <c r="L54" s="4"/>
+      <c r="L54" s="3"/>
       <c r="M54" s="1" t="n">
         <v>0.23</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="0" t="n">
+      <c r="B55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="C55" s="1" t="n">
@@ -2401,13 +2961,13 @@
         <f aca="false">K54 + (SUM(H$2:H54) * (J55-J54) * 100)</f>
         <v>-7527.2</v>
       </c>
-      <c r="L55" s="4"/>
+      <c r="L55" s="3"/>
       <c r="M55" s="1" t="n">
         <v>0.24</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="0" t="n">
+      <c r="B56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="C56" s="1" t="n">
@@ -2440,13 +3000,13 @@
         <f aca="false">K55 + (SUM(H$2:H55) * (J56-J55) * 100)</f>
         <v>-7994.4</v>
       </c>
-      <c r="L56" s="4"/>
+      <c r="L56" s="3"/>
       <c r="M56" s="1" t="n">
         <v>0.24</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="0" t="n">
+      <c r="B57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="C57" s="1" t="n">
@@ -2479,13 +3039,13 @@
         <f aca="false">K56 + (SUM(H$2:H56) * (J57-J56) * 100)</f>
         <v>-8480.8</v>
       </c>
-      <c r="L57" s="4"/>
+      <c r="L57" s="3"/>
       <c r="M57" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="0" t="n">
+      <c r="B58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="C58" s="1" t="n">
@@ -2518,13 +3078,13 @@
         <f aca="false">K57 + (SUM(H$2:H57) * (J58-J57) * 100)</f>
         <v>-8987.2</v>
       </c>
-      <c r="L58" s="4"/>
+      <c r="L58" s="3"/>
       <c r="M58" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="0" t="n">
+      <c r="B59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="C59" s="1" t="n">
@@ -2557,13 +3117,13 @@
         <f aca="false">K58 + (SUM(H$2:H58) * (J59-J58) * 100)</f>
         <v>-9513.6</v>
       </c>
-      <c r="L59" s="4"/>
+      <c r="L59" s="3"/>
       <c r="M59" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="0" t="n">
+      <c r="B60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="C60" s="1" t="n">
@@ -2596,13 +3156,13 @@
         <f aca="false">K59 + (SUM(H$2:H59) * (J60-J59) * 100)</f>
         <v>-10060.8</v>
       </c>
-      <c r="L60" s="4"/>
+      <c r="L60" s="3"/>
       <c r="M60" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="0" t="n">
+      <c r="B61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="C61" s="1" t="n">
@@ -2635,13 +3195,13 @@
         <f aca="false">K60 + (SUM(H$2:H60) * (J61-J60) * 100)</f>
         <v>-10628.8</v>
       </c>
-      <c r="L61" s="4"/>
+      <c r="L61" s="3"/>
       <c r="M61" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="0" t="n">
+      <c r="B62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="C62" s="1" t="n">
@@ -2674,13 +3234,13 @@
         <f aca="false">K61 + (SUM(H$2:H61) * (J62-J61) * 100)</f>
         <v>-11217.6</v>
       </c>
-      <c r="L62" s="4"/>
+      <c r="L62" s="3"/>
       <c r="M62" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="0" t="n">
+      <c r="B63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="C63" s="1" t="n">
@@ -2713,13 +3273,13 @@
         <f aca="false">K62 + (SUM(H$2:H62) * (J63-J62) * 100)</f>
         <v>-11827.2</v>
       </c>
-      <c r="L63" s="4"/>
+      <c r="L63" s="3"/>
       <c r="M63" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="0" t="n">
+      <c r="B64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="C64" s="1" t="n">
@@ -2752,13 +3312,13 @@
         <f aca="false">K63 + (SUM(H$2:H63) * (J64-J63) * 100)</f>
         <v>-12457.6</v>
       </c>
-      <c r="L64" s="4"/>
+      <c r="L64" s="3"/>
       <c r="M64" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="0" t="n">
+      <c r="B65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="C65" s="1" t="n">
@@ -2791,13 +3351,13 @@
         <f aca="false">K64 + (SUM(H$2:H64) * (J65-J64) * 100)</f>
         <v>-13108.8</v>
       </c>
-      <c r="L65" s="4"/>
+      <c r="L65" s="3"/>
       <c r="M65" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="0" t="n">
+      <c r="B66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="C66" s="1" t="n">
@@ -2830,13 +3390,13 @@
         <f aca="false">K65 + (SUM(H$2:H65) * (J66-J65) * 100)</f>
         <v>-13780.8</v>
       </c>
-      <c r="L66" s="4"/>
+      <c r="L66" s="3"/>
       <c r="M66" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="0" t="n">
+      <c r="B67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="C67" s="1" t="n">
@@ -2869,13 +3429,13 @@
         <f aca="false">K66 + (SUM(H$2:H66) * (J67-J66) * 100)</f>
         <v>-14473.6</v>
       </c>
-      <c r="L67" s="4"/>
+      <c r="L67" s="3"/>
       <c r="M67" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="0" t="n">
+      <c r="B68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="C68" s="1" t="n">
@@ -2908,13 +3468,13 @@
         <f aca="false">K67 + (SUM(H$2:H67) * (J68-J67) * 100)</f>
         <v>-15187.2</v>
       </c>
-      <c r="L68" s="4"/>
+      <c r="L68" s="3"/>
       <c r="M68" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="0" t="n">
+      <c r="B69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="C69" s="1" t="n">
@@ -2947,13 +3507,13 @@
         <f aca="false">K68 + (SUM(H$2:H68) * (J69-J68) * 100)</f>
         <v>-15921.6</v>
       </c>
-      <c r="L69" s="4"/>
+      <c r="L69" s="3"/>
       <c r="M69" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="0" t="n">
+      <c r="B70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="C70" s="1" t="n">
@@ -2986,13 +3546,13 @@
         <f aca="false">K69 + (SUM(H$2:H69) * (J70-J69) * 100)</f>
         <v>-16676.8</v>
       </c>
-      <c r="L70" s="4"/>
+      <c r="L70" s="3"/>
       <c r="M70" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="0" t="n">
+      <c r="B71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="C71" s="1" t="n">
@@ -3025,13 +3585,13 @@
         <f aca="false">K70 + (SUM(H$2:H70) * (J71-J70) * 100)</f>
         <v>-17452.8</v>
       </c>
-      <c r="L71" s="4"/>
+      <c r="L71" s="3"/>
       <c r="M71" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="0" t="n">
+      <c r="B72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="C72" s="1" t="n">
@@ -3064,13 +3624,13 @@
         <f aca="false">K71 + (SUM(H$2:H71) * (J72-J71) * 100)</f>
         <v>-18249.6</v>
       </c>
-      <c r="L72" s="4"/>
+      <c r="L72" s="3"/>
       <c r="M72" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="0" t="n">
+      <c r="B73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="C73" s="1" t="n">
@@ -3103,13 +3663,13 @@
         <f aca="false">K72 + (SUM(H$2:H72) * (J73-J72) * 100)</f>
         <v>-19067.2</v>
       </c>
-      <c r="L73" s="4"/>
+      <c r="L73" s="3"/>
       <c r="M73" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="0" t="n">
+      <c r="B74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="C74" s="1" t="n">
@@ -3142,13 +3702,13 @@
         <f aca="false">K73 + (SUM(H$2:H73) * (J74-J73) * 100)</f>
         <v>-19905.6</v>
       </c>
-      <c r="L74" s="4"/>
+      <c r="L74" s="3"/>
       <c r="M74" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="0" t="n">
+      <c r="B75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="C75" s="1" t="n">
@@ -3181,13 +3741,13 @@
         <f aca="false">K74 + (SUM(H$2:H74) * (J75-J74) * 100)</f>
         <v>-20764.8</v>
       </c>
-      <c r="L75" s="4"/>
+      <c r="L75" s="3"/>
       <c r="M75" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="0" t="n">
+      <c r="B76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="C76" s="1" t="n">
@@ -3220,13 +3780,13 @@
         <f aca="false">K75 + (SUM(H$2:H75) * (J76-J75) * 100)</f>
         <v>-21644.8</v>
       </c>
-      <c r="L76" s="4"/>
+      <c r="L76" s="3"/>
       <c r="M76" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="0" t="n">
+      <c r="B77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="C77" s="1" t="n">
@@ -3259,13 +3819,13 @@
         <f aca="false">K76 + (SUM(H$2:H76) * (J77-J76) * 100)</f>
         <v>-22545.6</v>
       </c>
-      <c r="L77" s="4"/>
+      <c r="L77" s="3"/>
       <c r="M77" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="0" t="n">
+      <c r="B78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="C78" s="1" t="n">
@@ -3298,13 +3858,13 @@
         <f aca="false">K77 + (SUM(H$2:H77) * (J78-J77) * 100)</f>
         <v>-23467.2</v>
       </c>
-      <c r="L78" s="4"/>
+      <c r="L78" s="3"/>
       <c r="M78" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="0" t="n">
+      <c r="B79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="C79" s="1" t="n">
@@ -3337,13 +3897,13 @@
         <f aca="false">K78 + (SUM(H$2:H78) * (J79-J78) * 100)</f>
         <v>-24409.6</v>
       </c>
-      <c r="L79" s="4"/>
+      <c r="L79" s="3"/>
       <c r="M79" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="0" t="n">
+      <c r="B80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="C80" s="1" t="n">
@@ -3376,13 +3936,13 @@
         <f aca="false">K79 + (SUM(H$2:H79) * (J80-J79) * 100)</f>
         <v>-25372.8</v>
       </c>
-      <c r="L80" s="4"/>
+      <c r="L80" s="3"/>
       <c r="M80" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="0" t="n">
+      <c r="B81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="C81" s="1" t="n">
@@ -3415,13 +3975,13 @@
         <f aca="false">K80 + (SUM(H$2:H80) * (J81-J80) * 100)</f>
         <v>-26356.8</v>
       </c>
-      <c r="L81" s="4"/>
+      <c r="L81" s="3"/>
       <c r="M81" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="0" t="n">
+      <c r="B82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="C82" s="1" t="n">
@@ -3454,13 +4014,13 @@
         <f aca="false">K81 + (SUM(H$2:H81) * (J82-J81) * 100)</f>
         <v>-27361.6</v>
       </c>
-      <c r="L82" s="4"/>
+      <c r="L82" s="3"/>
       <c r="M82" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="0" t="n">
+      <c r="B83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="C83" s="1" t="n">
@@ -3493,13 +4053,13 @@
         <f aca="false">K82 + (SUM(H$2:H82) * (J83-J82) * 100)</f>
         <v>-28387.2</v>
       </c>
-      <c r="L83" s="4"/>
+      <c r="L83" s="3"/>
       <c r="M83" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="0" t="n">
+      <c r="B84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="C84" s="1" t="n">
@@ -3532,13 +4092,13 @@
         <f aca="false">K83 + (SUM(H$2:H83) * (J84-J83) * 100)</f>
         <v>-29433.6</v>
       </c>
-      <c r="L84" s="4"/>
+      <c r="L84" s="3"/>
       <c r="M84" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="0" t="n">
+      <c r="B85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="C85" s="1" t="n">
@@ -3571,13 +4131,13 @@
         <f aca="false">K84 + (SUM(H$2:H84) * (J85-J84) * 100)</f>
         <v>-30500.8</v>
       </c>
-      <c r="L85" s="4"/>
+      <c r="L85" s="3"/>
       <c r="M85" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="0" t="n">
+      <c r="B86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="C86" s="1" t="n">
@@ -3610,13 +4170,13 @@
         <f aca="false">K85 + (SUM(H$2:H85) * (J86-J85) * 100)</f>
         <v>-31588.8</v>
       </c>
-      <c r="L86" s="4"/>
+      <c r="L86" s="3"/>
       <c r="M86" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="0" t="n">
+      <c r="B87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="C87" s="1" t="n">
@@ -3649,13 +4209,13 @@
         <f aca="false">K86 + (SUM(H$2:H86) * (J87-J86) * 100)</f>
         <v>-32697.6</v>
       </c>
-      <c r="L87" s="4"/>
+      <c r="L87" s="3"/>
       <c r="M87" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="0" t="n">
+      <c r="B88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="C88" s="1" t="n">
@@ -3688,13 +4248,13 @@
         <f aca="false">K87 + (SUM(H$2:H87) * (J88-J87) * 100)</f>
         <v>-33827.2</v>
       </c>
-      <c r="L88" s="4"/>
+      <c r="L88" s="3"/>
       <c r="M88" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="0" t="n">
+      <c r="B89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="C89" s="1" t="n">
@@ -3727,13 +4287,13 @@
         <f aca="false">K88 + (SUM(H$2:H88) * (J89-J88) * 100)</f>
         <v>-34977.6</v>
       </c>
-      <c r="L89" s="4"/>
+      <c r="L89" s="3"/>
       <c r="M89" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="0" t="n">
+      <c r="B90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="C90" s="1" t="n">
@@ -3766,13 +4326,13 @@
         <f aca="false">K89 + (SUM(H$2:H89) * (J90-J89) * 100)</f>
         <v>-36148.8</v>
       </c>
-      <c r="L90" s="4"/>
+      <c r="L90" s="3"/>
       <c r="M90" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="0" t="n">
+      <c r="B91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="C91" s="1" t="n">
@@ -3805,13 +4365,13 @@
         <f aca="false">K90 + (SUM(H$2:H90) * (J91-J90) * 100)</f>
         <v>-37340.8</v>
       </c>
-      <c r="L91" s="4"/>
+      <c r="L91" s="3"/>
       <c r="M91" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="0" t="n">
+      <c r="B92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="C92" s="1" t="n">
@@ -3844,13 +4404,13 @@
         <f aca="false">K91 + (SUM(H$2:H91) * (J92-J91) * 100)</f>
         <v>-38553.6</v>
       </c>
-      <c r="L92" s="4"/>
+      <c r="L92" s="3"/>
       <c r="M92" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="0" t="n">
+      <c r="B93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="C93" s="1" t="n">
@@ -3883,13 +4443,13 @@
         <f aca="false">K92 + (SUM(H$2:H92) * (J93-J92) * 100)</f>
         <v>-39787.2</v>
       </c>
-      <c r="L93" s="4"/>
+      <c r="L93" s="3"/>
       <c r="M93" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="0" t="n">
+      <c r="B94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="C94" s="1" t="n">
@@ -3922,13 +4482,13 @@
         <f aca="false">K93 + (SUM(H$2:H93) * (J94-J93) * 100)</f>
         <v>-41041.6</v>
       </c>
-      <c r="L94" s="4"/>
+      <c r="L94" s="3"/>
       <c r="M94" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="0" t="n">
+      <c r="B95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="C95" s="1" t="n">
@@ -3961,13 +4521,13 @@
         <f aca="false">K94 + (SUM(H$2:H94) * (J95-J94) * 100)</f>
         <v>-42316.8</v>
       </c>
-      <c r="L95" s="4"/>
+      <c r="L95" s="3"/>
       <c r="M95" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="0" t="n">
+      <c r="B96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="C96" s="1" t="n">
@@ -4000,13 +4560,13 @@
         <f aca="false">K95 + (SUM(H$2:H95) * (J96-J95) * 100)</f>
         <v>-43612.8</v>
       </c>
-      <c r="L96" s="4"/>
+      <c r="L96" s="3"/>
       <c r="M96" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="0" t="n">
+      <c r="B97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="C97" s="1" t="n">
@@ -4039,13 +4599,13 @@
         <f aca="false">K96 + (SUM(H$2:H96) * (J97-J96) * 100)</f>
         <v>-44929.6</v>
       </c>
-      <c r="L97" s="4"/>
+      <c r="L97" s="3"/>
       <c r="M97" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="0" t="n">
+      <c r="B98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="C98" s="1" t="n">
@@ -4078,13 +4638,13 @@
         <f aca="false">K97 + (SUM(H$2:H97) * (J98-J97) * 100)</f>
         <v>-46267.2</v>
       </c>
-      <c r="L98" s="4"/>
+      <c r="L98" s="3"/>
       <c r="M98" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="0" t="n">
+      <c r="B99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="C99" s="1" t="n">
@@ -4117,13 +4677,13 @@
         <f aca="false">K98 + (SUM(H$2:H98) * (J99-J98) * 100)</f>
         <v>-47625.6</v>
       </c>
-      <c r="L99" s="4"/>
+      <c r="L99" s="3"/>
       <c r="M99" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="0" t="n">
+      <c r="B100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="C100" s="1" t="n">
@@ -4156,13 +4716,13 @@
         <f aca="false">K99 + (SUM(H$2:H99) * (J100-J99) * 100)</f>
         <v>-49004.8</v>
       </c>
-      <c r="L100" s="4"/>
+      <c r="L100" s="3"/>
       <c r="M100" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="0" t="n">
+      <c r="B101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="C101" s="1" t="n">
@@ -4195,13 +4755,13 @@
         <f aca="false">K100 + (SUM(H$2:H100) * (J101-J100) * 100)</f>
         <v>-50404.8</v>
       </c>
-      <c r="L101" s="4"/>
+      <c r="L101" s="3"/>
       <c r="M101" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="0" t="n">
+      <c r="B102" s="2" t="n">
         <v>101</v>
       </c>
       <c r="C102" s="1" t="n">
@@ -4234,13 +4794,13 @@
         <f aca="false">K101 + (SUM(H$2:H101) * (J102-J101) * 100)</f>
         <v>-51825.6</v>
       </c>
-      <c r="L102" s="4"/>
+      <c r="L102" s="3"/>
       <c r="M102" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="0" t="n">
+      <c r="B103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="C103" s="1" t="n">
@@ -4273,13 +4833,13 @@
         <f aca="false">K102 + (SUM(H$2:H102) * (J103-J102) * 100)</f>
         <v>-53267.2</v>
       </c>
-      <c r="L103" s="4"/>
+      <c r="L103" s="3"/>
       <c r="M103" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="0" t="n">
+      <c r="B104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="C104" s="1" t="n">
@@ -4312,13 +4872,13 @@
         <f aca="false">K103 + (SUM(H$2:H103) * (J104-J103) * 100)</f>
         <v>-54729.6</v>
       </c>
-      <c r="L104" s="4"/>
+      <c r="L104" s="3"/>
       <c r="M104" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="0" t="n">
+      <c r="B105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="C105" s="1" t="n">
@@ -4351,13 +4911,13 @@
         <f aca="false">K104 + (SUM(H$2:H104) * (J105-J104) * 100)</f>
         <v>-56212.8</v>
       </c>
-      <c r="L105" s="4"/>
+      <c r="L105" s="3"/>
       <c r="M105" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="0" t="n">
+      <c r="B106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="C106" s="1" t="n">
@@ -4390,13 +4950,13 @@
         <f aca="false">K105 + (SUM(H$2:H105) * (J106-J105) * 100)</f>
         <v>-57716.8</v>
       </c>
-      <c r="L106" s="4"/>
+      <c r="L106" s="3"/>
       <c r="M106" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="0" t="n">
+      <c r="B107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="C107" s="1" t="n">
@@ -4429,13 +4989,13 @@
         <f aca="false">K106 + (SUM(H$2:H106) * (J107-J106) * 100)</f>
         <v>-59241.6</v>
       </c>
-      <c r="L107" s="4"/>
+      <c r="L107" s="3"/>
       <c r="M107" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="0" t="n">
+      <c r="B108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="C108" s="1" t="n">
@@ -4468,13 +5028,13 @@
         <f aca="false">K107 + (SUM(H$2:H107) * (J108-J107) * 100)</f>
         <v>-60787.2</v>
       </c>
-      <c r="L108" s="4"/>
+      <c r="L108" s="3"/>
       <c r="M108" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="0" t="n">
+      <c r="B109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="C109" s="1" t="n">
@@ -4507,13 +5067,13 @@
         <f aca="false">K108 + (SUM(H$2:H108) * (J109-J108) * 100)</f>
         <v>-62353.6</v>
       </c>
-      <c r="L109" s="4"/>
+      <c r="L109" s="3"/>
       <c r="M109" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="0" t="n">
+      <c r="B110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="C110" s="1" t="n">
@@ -4546,13 +5106,13 @@
         <f aca="false">K109 + (SUM(H$2:H109) * (J110-J109) * 100)</f>
         <v>-63940.8</v>
       </c>
-      <c r="L110" s="4"/>
+      <c r="L110" s="3"/>
       <c r="M110" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="0" t="n">
+      <c r="B111" s="2" t="n">
         <v>110</v>
       </c>
       <c r="C111" s="1" t="n">
@@ -4585,13 +5145,13 @@
         <f aca="false">K110 + (SUM(H$2:H110) * (J111-J110) * 100)</f>
         <v>-65548.8</v>
       </c>
-      <c r="L111" s="4"/>
+      <c r="L111" s="3"/>
       <c r="M111" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="0" t="n">
+      <c r="B112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="C112" s="1" t="n">
@@ -4624,13 +5184,13 @@
         <f aca="false">K111 + (SUM(H$2:H111) * (J112-J111) * 100)</f>
         <v>-67177.6</v>
       </c>
-      <c r="L112" s="4"/>
+      <c r="L112" s="3"/>
       <c r="M112" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="0" t="n">
+      <c r="B113" s="2" t="n">
         <v>112</v>
       </c>
       <c r="C113" s="1" t="n">
@@ -4663,13 +5223,13 @@
         <f aca="false">K112 + (SUM(H$2:H112) * (J113-J112) * 100)</f>
         <v>-68827.2</v>
       </c>
-      <c r="L113" s="4"/>
+      <c r="L113" s="3"/>
       <c r="M113" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="0" t="n">
+      <c r="B114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="C114" s="1" t="n">
@@ -4702,13 +5262,13 @@
         <f aca="false">K113 + (SUM(H$2:H113) * (J114-J113) * 100)</f>
         <v>-70497.6</v>
       </c>
-      <c r="L114" s="4"/>
+      <c r="L114" s="3"/>
       <c r="M114" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="0" t="n">
+      <c r="B115" s="2" t="n">
         <v>114</v>
       </c>
       <c r="C115" s="1" t="n">
@@ -4741,13 +5301,13 @@
         <f aca="false">K114 + (SUM(H$2:H114) * (J115-J114) * 100)</f>
         <v>-72188.8</v>
       </c>
-      <c r="L115" s="4"/>
+      <c r="L115" s="3"/>
       <c r="M115" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="0" t="n">
+      <c r="B116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="C116" s="1" t="n">
@@ -4780,13 +5340,13 @@
         <f aca="false">K115 + (SUM(H$2:H115) * (J116-J115) * 100)</f>
         <v>-73900.8</v>
       </c>
-      <c r="L116" s="4"/>
+      <c r="L116" s="3"/>
       <c r="M116" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="0" t="n">
+      <c r="B117" s="2" t="n">
         <v>116</v>
       </c>
       <c r="C117" s="1" t="n">
@@ -4819,13 +5379,13 @@
         <f aca="false">K116 + (SUM(H$2:H116) * (J117-J116) * 100)</f>
         <v>-75633.6</v>
       </c>
-      <c r="L117" s="4"/>
+      <c r="L117" s="3"/>
       <c r="M117" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="0" t="n">
+      <c r="B118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="C118" s="1" t="n">
@@ -4858,13 +5418,13 @@
         <f aca="false">K117 + (SUM(H$2:H117) * (J118-J117) * 100)</f>
         <v>-77387.2</v>
       </c>
-      <c r="L118" s="4"/>
+      <c r="L118" s="3"/>
       <c r="M118" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B119" s="0" t="n">
+      <c r="B119" s="2" t="n">
         <v>118</v>
       </c>
       <c r="C119" s="1" t="n">
@@ -4897,13 +5457,13 @@
         <f aca="false">K118 + (SUM(H$2:H118) * (J119-J118) * 100)</f>
         <v>-79161.6</v>
       </c>
-      <c r="L119" s="4"/>
+      <c r="L119" s="3"/>
       <c r="M119" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="0" t="n">
+      <c r="B120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="C120" s="1" t="n">
@@ -4936,13 +5496,13 @@
         <f aca="false">K119 + (SUM(H$2:H119) * (J120-J119) * 100)</f>
         <v>-80956.8</v>
       </c>
-      <c r="L120" s="4"/>
+      <c r="L120" s="3"/>
       <c r="M120" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B121" s="0" t="n">
+      <c r="B121" s="2" t="n">
         <v>120</v>
       </c>
       <c r="C121" s="1" t="n">
@@ -4975,13 +5535,13 @@
         <f aca="false">K120 + (SUM(H$2:H120) * (J121-J120) * 100)</f>
         <v>-82772.8</v>
       </c>
-      <c r="L121" s="4"/>
+      <c r="L121" s="3"/>
       <c r="M121" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B122" s="0" t="n">
+      <c r="B122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="C122" s="1" t="n">
@@ -5014,13 +5574,13 @@
         <f aca="false">K121 + (SUM(H$2:H121) * (J122-J121) * 100)</f>
         <v>-84609.6</v>
       </c>
-      <c r="L122" s="4"/>
+      <c r="L122" s="3"/>
       <c r="M122" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="0" t="n">
+      <c r="B123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="C123" s="1" t="n">
@@ -5053,13 +5613,13 @@
         <f aca="false">K122 + (SUM(H$2:H122) * (J123-J122) * 100)</f>
         <v>-86467.2</v>
       </c>
-      <c r="L123" s="4"/>
+      <c r="L123" s="3"/>
       <c r="M123" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="0" t="n">
+      <c r="B124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="C124" s="1" t="n">
@@ -5092,13 +5652,13 @@
         <f aca="false">K123 + (SUM(H$2:H123) * (J124-J123) * 100)</f>
         <v>-88345.6</v>
       </c>
-      <c r="L124" s="4"/>
+      <c r="L124" s="3"/>
       <c r="M124" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="0" t="n">
+      <c r="B125" s="2" t="n">
         <v>124</v>
       </c>
       <c r="C125" s="1" t="n">
@@ -5131,13 +5691,13 @@
         <f aca="false">K124 + (SUM(H$2:H124) * (J125-J124) * 100)</f>
         <v>-90244.8</v>
       </c>
-      <c r="L125" s="4"/>
+      <c r="L125" s="3"/>
       <c r="M125" s="1" t="n">
         <v>0.26</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="0" t="n">
+      <c r="B126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="C126" s="1" t="n">
@@ -5158,7 +5718,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="0" t="n">
+      <c r="B127" s="2" t="n">
         <v>126</v>
       </c>
       <c r="C127" s="1" t="n">
@@ -5179,7 +5739,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B128" s="0" t="n">
+      <c r="B128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="C128" s="1" t="n">
@@ -5200,7 +5760,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B129" s="0" t="n">
+      <c r="B129" s="2" t="n">
         <v>128</v>
       </c>
       <c r="C129" s="1" t="n">
@@ -5221,7 +5781,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="0" t="n">
+      <c r="B130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="C130" s="1" t="n">
@@ -5242,7 +5802,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B131" s="0" t="n">
+      <c r="B131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="C131" s="1" t="n">
@@ -5263,7 +5823,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B132" s="0" t="n">
+      <c r="B132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="C132" s="1" t="n">
@@ -5284,7 +5844,7 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B133" s="0" t="n">
+      <c r="B133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="C133" s="1" t="n">
@@ -5305,7 +5865,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="0" t="n">
+      <c r="B134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="C134" s="1" t="n">
@@ -5326,7 +5886,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B135" s="0" t="n">
+      <c r="B135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="C135" s="1" t="n">
@@ -5347,7 +5907,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B136" s="0" t="n">
+      <c r="B136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="C136" s="1" t="n">
@@ -5368,7 +5928,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="0" t="n">
+      <c r="B137" s="2" t="n">
         <v>136</v>
       </c>
       <c r="C137" s="1" t="n">
@@ -5389,7 +5949,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="0" t="n">
+      <c r="B138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="C138" s="1" t="n">
@@ -5410,7 +5970,7 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="0" t="n">
+      <c r="B139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="C139" s="1" t="n">
@@ -5431,7 +5991,7 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="0" t="n">
+      <c r="B140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="C140" s="1" t="n">
@@ -5452,7 +6012,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B141" s="0" t="n">
+      <c r="B141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="C141" s="1" t="n">
@@ -5473,7 +6033,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B142" s="0" t="n">
+      <c r="B142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="C142" s="1" t="n">
@@ -5494,7 +6054,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B143" s="0" t="n">
+      <c r="B143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="C143" s="1" t="n">
@@ -5515,7 +6075,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B144" s="0" t="n">
+      <c r="B144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="C144" s="1" t="n">
@@ -5536,7 +6096,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B145" s="0" t="n">
+      <c r="B145" s="2" t="n">
         <v>144</v>
       </c>
       <c r="C145" s="1" t="n">
@@ -5557,7 +6117,7 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B146" s="0" t="n">
+      <c r="B146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="C146" s="1" t="n">
@@ -5578,7 +6138,7 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B147" s="0" t="n">
+      <c r="B147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="C147" s="1" t="n">
@@ -5599,7 +6159,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B148" s="0" t="n">
+      <c r="B148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="C148" s="1" t="n">
@@ -5620,7 +6180,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B149" s="0" t="n">
+      <c r="B149" s="2" t="n">
         <v>148</v>
       </c>
       <c r="C149" s="1" t="n">
@@ -5641,7 +6201,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B150" s="0" t="n">
+      <c r="B150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="C150" s="1" t="n">
@@ -5662,7 +6222,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B151" s="0" t="n">
+      <c r="B151" s="2" t="n">
         <v>150</v>
       </c>
       <c r="C151" s="1" t="n">
@@ -5683,7 +6243,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B152" s="0" t="n">
+      <c r="B152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="C152" s="1" t="n">
@@ -5704,7 +6264,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B153" s="0" t="n">
+      <c r="B153" s="2" t="n">
         <v>152</v>
       </c>
       <c r="C153" s="1" t="n">
@@ -5725,7 +6285,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B154" s="0" t="n">
+      <c r="B154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="C154" s="1" t="n">
@@ -5746,7 +6306,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B155" s="0" t="n">
+      <c r="B155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="C155" s="1" t="n">
@@ -5767,7 +6327,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B156" s="0" t="n">
+      <c r="B156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="C156" s="1" t="n">
@@ -5788,7 +6348,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B157" s="0" t="n">
+      <c r="B157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="C157" s="1" t="n">
@@ -5809,7 +6369,7 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B158" s="0" t="n">
+      <c r="B158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="C158" s="1" t="n">
@@ -5830,7 +6390,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B159" s="0" t="n">
+      <c r="B159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="C159" s="1" t="n">
@@ -5851,7 +6411,7 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B160" s="0" t="n">
+      <c r="B160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="C160" s="1" t="n">
@@ -5872,7 +6432,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B161" s="0" t="n">
+      <c r="B161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="C161" s="1" t="n">
@@ -5893,7 +6453,7 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B162" s="0" t="n">
+      <c r="B162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="C162" s="1" t="n">
@@ -5914,7 +6474,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B163" s="0" t="n">
+      <c r="B163" s="2" t="n">
         <v>162</v>
       </c>
       <c r="C163" s="1" t="n">
@@ -5935,7 +6495,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B164" s="0" t="n">
+      <c r="B164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="C164" s="1" t="n">
@@ -5956,7 +6516,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B165" s="0" t="n">
+      <c r="B165" s="2" t="n">
         <v>164</v>
       </c>
       <c r="C165" s="1" t="n">
@@ -5977,7 +6537,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B166" s="0" t="n">
+      <c r="B166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="C166" s="1" t="n">
@@ -5998,7 +6558,7 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B167" s="0" t="n">
+      <c r="B167" s="2" t="n">
         <v>166</v>
       </c>
       <c r="C167" s="1" t="n">
@@ -6019,7 +6579,7 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B168" s="0" t="n">
+      <c r="B168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="C168" s="1" t="n">
@@ -6040,7 +6600,7 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B169" s="0" t="n">
+      <c r="B169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="C169" s="1" t="n">
@@ -6061,7 +6621,7 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B170" s="0" t="n">
+      <c r="B170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="C170" s="1" t="n">
@@ -6082,7 +6642,7 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B171" s="0" t="n">
+      <c r="B171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="C171" s="1" t="n">
@@ -6103,7 +6663,7 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B172" s="0" t="n">
+      <c r="B172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="C172" s="1" t="n">
@@ -6124,7 +6684,7 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B173" s="0" t="n">
+      <c r="B173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="C173" s="1" t="n">
@@ -6145,7 +6705,7 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B174" s="0" t="n">
+      <c r="B174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="C174" s="1" t="n">
@@ -6166,7 +6726,7 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B175" s="0" t="n">
+      <c r="B175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="C175" s="1" t="n">
@@ -6187,7 +6747,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B176" s="0" t="n">
+      <c r="B176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="C176" s="1" t="n">
@@ -6208,7 +6768,7 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B177" s="0" t="n">
+      <c r="B177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="C177" s="1" t="n">
@@ -6229,7 +6789,7 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B178" s="0" t="n">
+      <c r="B178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="C178" s="1" t="n">
@@ -6250,7 +6810,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B179" s="0" t="n">
+      <c r="B179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="C179" s="1" t="n">
@@ -6271,7 +6831,7 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B180" s="0" t="n">
+      <c r="B180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="C180" s="1" t="n">
@@ -6292,7 +6852,7 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B181" s="0" t="n">
+      <c r="B181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="C181" s="1" t="n">
@@ -6313,7 +6873,7 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B182" s="0" t="n">
+      <c r="B182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="C182" s="1" t="n">
@@ -6334,7 +6894,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B183" s="0" t="n">
+      <c r="B183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="C183" s="1" t="n">
@@ -6355,7 +6915,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B184" s="0" t="n">
+      <c r="B184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="C184" s="1" t="n">
@@ -6376,7 +6936,7 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B185" s="0" t="n">
+      <c r="B185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="C185" s="1" t="n">
@@ -6397,7 +6957,7 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B186" s="0" t="n">
+      <c r="B186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="C186" s="1" t="n">
@@ -6418,7 +6978,7 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B187" s="0" t="n">
+      <c r="B187" s="2" t="n">
         <v>186</v>
       </c>
       <c r="C187" s="1" t="n">
@@ -6439,7 +6999,7 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B188" s="0" t="n">
+      <c r="B188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="C188" s="1" t="n">
@@ -6460,7 +7020,7 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B189" s="0" t="n">
+      <c r="B189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="C189" s="1" t="n">
@@ -6481,7 +7041,7 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B190" s="0" t="n">
+      <c r="B190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="C190" s="1" t="n">
@@ -6502,7 +7062,7 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B191" s="0" t="n">
+      <c r="B191" s="2" t="n">
         <v>190</v>
       </c>
       <c r="C191" s="1" t="n">
@@ -6523,7 +7083,7 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B192" s="0" t="n">
+      <c r="B192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="C192" s="1" t="n">
@@ -6544,7 +7104,7 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B193" s="0" t="n">
+      <c r="B193" s="2" t="n">
         <v>192</v>
       </c>
       <c r="C193" s="1" t="n">
@@ -6565,7 +7125,7 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B194" s="0" t="n">
+      <c r="B194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="C194" s="1" t="n">
@@ -6586,7 +7146,7 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B195" s="0" t="n">
+      <c r="B195" s="2" t="n">
         <v>194</v>
       </c>
       <c r="C195" s="1" t="n">
@@ -6607,7 +7167,7 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B196" s="0" t="n">
+      <c r="B196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="C196" s="1" t="n">
@@ -6628,7 +7188,7 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B197" s="0" t="n">
+      <c r="B197" s="2" t="n">
         <v>196</v>
       </c>
       <c r="C197" s="1" t="n">
@@ -6649,7 +7209,7 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B198" s="0" t="n">
+      <c r="B198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="C198" s="1" t="n">
@@ -6670,7 +7230,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B199" s="0" t="n">
+      <c r="B199" s="2" t="n">
         <v>198</v>
       </c>
       <c r="C199" s="1" t="n">
@@ -6691,7 +7251,7 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B200" s="0" t="n">
+      <c r="B200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="C200" s="1" t="n">
@@ -6712,7 +7272,7 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B201" s="0" t="n">
+      <c r="B201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="C201" s="1" t="n">
@@ -6749,10 +7309,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E201"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -6769,7 +7329,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
@@ -6789,7 +7349,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="n">
@@ -6810,7 +7370,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="n">
@@ -6831,7 +7391,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="n">
@@ -6852,7 +7412,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="n">
@@ -6873,7 +7433,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="n">
@@ -6894,7 +7454,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="n">
@@ -6915,7 +7475,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="n">
@@ -6936,7 +7496,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="n">
@@ -6957,7 +7517,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="n">
@@ -6978,7 +7538,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="n">
@@ -6999,7 +7559,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="n">
@@ -7020,7 +7580,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
@@ -7041,7 +7601,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="n">
@@ -7062,7 +7622,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="n">
@@ -7083,7 +7643,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="n">
@@ -7104,7 +7664,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="n">
@@ -7125,7 +7685,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="n">
@@ -7146,7 +7706,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="n">
@@ -7167,7 +7727,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="n">
@@ -7188,7 +7748,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="n">
@@ -7209,7 +7769,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="n">
@@ -7230,7 +7790,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+      <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="n">
@@ -7251,7 +7811,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+      <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="n">
@@ -7272,7 +7832,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
+      <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -7293,7 +7853,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="n">
+      <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -7314,7 +7874,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="n">
+      <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="n">
@@ -7335,7 +7895,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="n">
+      <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="n">
@@ -7356,7 +7916,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="n">
+      <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="n">
@@ -7377,7 +7937,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="n">
+      <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="n">
@@ -7398,7 +7958,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="n">
+      <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="n">
@@ -7419,7 +7979,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="n">
+      <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="n">
@@ -7440,7 +8000,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="n">
+      <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="n">
@@ -7461,7 +8021,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="n">
+      <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="n">
@@ -7482,7 +8042,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="n">
+      <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="n">
@@ -7503,7 +8063,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="n">
+      <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="n">
@@ -7524,7 +8084,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="n">
+      <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="n">
@@ -7545,7 +8105,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="n">
+      <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="n">
@@ -7566,7 +8126,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="n">
+      <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="n">
@@ -7587,7 +8147,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="n">
+      <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="n">
@@ -7608,7 +8168,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="n">
+      <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="n">
@@ -7629,7 +8189,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="n">
+      <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="n">
@@ -7650,7 +8210,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="n">
+      <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="n">
@@ -7671,7 +8231,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="n">
+      <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="n">
@@ -7692,7 +8252,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="n">
+      <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="n">
@@ -7713,7 +8273,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="n">
+      <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="n">
@@ -7734,7 +8294,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="n">
+      <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="n">
@@ -7755,7 +8315,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="n">
+      <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="n">
@@ -7776,7 +8336,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="n">
+      <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="n">
@@ -7797,7 +8357,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="n">
+      <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="n">
@@ -7818,7 +8378,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="n">
+      <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="n">
@@ -7837,7 +8397,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="n">
+      <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="n">
@@ -7856,7 +8416,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="0" t="n">
+      <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="n">
@@ -7875,7 +8435,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="0" t="n">
+      <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="n">
@@ -7894,7 +8454,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="n">
+      <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="n">
@@ -7913,7 +8473,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="n">
+      <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="n">
@@ -7932,7 +8492,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="n">
+      <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="n">
@@ -7951,7 +8511,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="n">
+      <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="n">
@@ -7970,7 +8530,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="n">
+      <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="n">
@@ -7989,7 +8549,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="n">
+      <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="n">
@@ -8008,7 +8568,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="n">
+      <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="n">
@@ -8027,7 +8587,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="n">
+      <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="n">
@@ -8046,7 +8606,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="n">
+      <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="n">
@@ -8065,7 +8625,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="n">
+      <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="n">
@@ -8084,7 +8644,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="n">
+      <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="n">
@@ -8103,7 +8663,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="n">
+      <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="n">
@@ -8122,7 +8682,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="n">
+      <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="n">
@@ -8141,7 +8701,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="n">
+      <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="n">
@@ -8160,7 +8720,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="n">
+      <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="n">
@@ -8179,7 +8739,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="n">
+      <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="n">
@@ -8198,7 +8758,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="0" t="n">
+      <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="n">
@@ -8217,7 +8777,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="0" t="n">
+      <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="n">
@@ -8236,7 +8796,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="0" t="n">
+      <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="n">
@@ -8255,7 +8815,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="n">
+      <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="n">
@@ -8274,7 +8834,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="n">
+      <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="n">
@@ -8293,7 +8853,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="n">
+      <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="n">
@@ -8312,7 +8872,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="n">
+      <c r="A78" s="2" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="n">
@@ -8331,7 +8891,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="n">
+      <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="n">
@@ -8350,7 +8910,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="0" t="n">
+      <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="n">
@@ -8369,7 +8929,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="0" t="n">
+      <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="n">
@@ -8388,7 +8948,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="n">
+      <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="n">
@@ -8407,7 +8967,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="n">
+      <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="n">
@@ -8426,7 +8986,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="n">
+      <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="n">
@@ -8445,7 +9005,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="0" t="n">
+      <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="n">
@@ -8464,7 +9024,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="0" t="n">
+      <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="n">
@@ -8483,7 +9043,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="0" t="n">
+      <c r="A87" s="2" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="n">
@@ -8502,7 +9062,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="0" t="n">
+      <c r="A88" s="2" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="n">
@@ -8521,7 +9081,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="0" t="n">
+      <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="n">
@@ -8540,7 +9100,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="0" t="n">
+      <c r="A90" s="2" t="n">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="n">
@@ -8559,7 +9119,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="0" t="n">
+      <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="n">
@@ -8578,7 +9138,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="0" t="n">
+      <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="n">
@@ -8597,7 +9157,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="0" t="n">
+      <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="n">
@@ -8616,7 +9176,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="0" t="n">
+      <c r="A94" s="2" t="n">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="n">
@@ -8635,7 +9195,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="0" t="n">
+      <c r="A95" s="2" t="n">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="n">
@@ -8654,7 +9214,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="0" t="n">
+      <c r="A96" s="2" t="n">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="n">
@@ -8673,7 +9233,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="0" t="n">
+      <c r="A97" s="2" t="n">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="n">
@@ -8692,7 +9252,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="0" t="n">
+      <c r="A98" s="2" t="n">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="n">
@@ -8711,7 +9271,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="0" t="n">
+      <c r="A99" s="2" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="n">
@@ -8730,7 +9290,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="0" t="n">
+      <c r="A100" s="2" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="n">
@@ -8749,7 +9309,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="0" t="n">
+      <c r="A101" s="2" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="n">
@@ -8768,7 +9328,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="0" t="n">
+      <c r="A102" s="2" t="n">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="n">
@@ -8787,7 +9347,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="0" t="n">
+      <c r="A103" s="2" t="n">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="n">
@@ -8806,7 +9366,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="0" t="n">
+      <c r="A104" s="2" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="n">
@@ -8825,7 +9385,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="0" t="n">
+      <c r="A105" s="2" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="n">
@@ -8844,7 +9404,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="0" t="n">
+      <c r="A106" s="2" t="n">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="n">
@@ -8863,7 +9423,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="0" t="n">
+      <c r="A107" s="2" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="1" t="n">
@@ -8882,7 +9442,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="0" t="n">
+      <c r="A108" s="2" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="1" t="n">
@@ -8901,7 +9461,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="0" t="n">
+      <c r="A109" s="2" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="1" t="n">
@@ -8920,7 +9480,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="0" t="n">
+      <c r="A110" s="2" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="1" t="n">
@@ -8939,7 +9499,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="0" t="n">
+      <c r="A111" s="2" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="1" t="n">
@@ -8958,7 +9518,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="0" t="n">
+      <c r="A112" s="2" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="1" t="n">
@@ -8977,7 +9537,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="0" t="n">
+      <c r="A113" s="2" t="n">
         <v>112</v>
       </c>
       <c r="B113" s="1" t="n">
@@ -8996,7 +9556,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="0" t="n">
+      <c r="A114" s="2" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="1" t="n">
@@ -9015,7 +9575,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="0" t="n">
+      <c r="A115" s="2" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="1" t="n">
@@ -9034,7 +9594,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="0" t="n">
+      <c r="A116" s="2" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="1" t="n">
@@ -9053,7 +9613,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="0" t="n">
+      <c r="A117" s="2" t="n">
         <v>116</v>
       </c>
       <c r="B117" s="1" t="n">
@@ -9072,7 +9632,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="n">
+      <c r="A118" s="2" t="n">
         <v>117</v>
       </c>
       <c r="B118" s="1" t="n">
@@ -9091,7 +9651,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="0" t="n">
+      <c r="A119" s="2" t="n">
         <v>118</v>
       </c>
       <c r="B119" s="1" t="n">
@@ -9110,7 +9670,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="0" t="n">
+      <c r="A120" s="2" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="1" t="n">
@@ -9129,7 +9689,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="0" t="n">
+      <c r="A121" s="2" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="1" t="n">
@@ -9148,7 +9708,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="0" t="n">
+      <c r="A122" s="2" t="n">
         <v>121</v>
       </c>
       <c r="B122" s="1" t="n">
@@ -9167,7 +9727,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="0" t="n">
+      <c r="A123" s="2" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="1" t="n">
@@ -9186,7 +9746,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="0" t="n">
+      <c r="A124" s="2" t="n">
         <v>123</v>
       </c>
       <c r="B124" s="1" t="n">
@@ -9205,7 +9765,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="0" t="n">
+      <c r="A125" s="2" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="1" t="n">
@@ -9224,7 +9784,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="0" t="n">
+      <c r="A126" s="2" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="1" t="n">
@@ -9243,7 +9803,7 @@
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="0" t="n">
+      <c r="A127" s="2" t="n">
         <v>126</v>
       </c>
       <c r="B127" s="1" t="n">
@@ -9262,7 +9822,7 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="0" t="n">
+      <c r="A128" s="2" t="n">
         <v>127</v>
       </c>
       <c r="B128" s="1" t="n">
@@ -9281,7 +9841,7 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="0" t="n">
+      <c r="A129" s="2" t="n">
         <v>128</v>
       </c>
       <c r="B129" s="1" t="n">
@@ -9300,7 +9860,7 @@
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="0" t="n">
+      <c r="A130" s="2" t="n">
         <v>129</v>
       </c>
       <c r="B130" s="1" t="n">
@@ -9319,7 +9879,7 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="0" t="n">
+      <c r="A131" s="2" t="n">
         <v>130</v>
       </c>
       <c r="B131" s="1" t="n">
@@ -9338,7 +9898,7 @@
       </c>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="0" t="n">
+      <c r="A132" s="2" t="n">
         <v>131</v>
       </c>
       <c r="B132" s="1" t="n">
@@ -9357,7 +9917,7 @@
       </c>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="0" t="n">
+      <c r="A133" s="2" t="n">
         <v>132</v>
       </c>
       <c r="B133" s="1" t="n">
@@ -9376,7 +9936,7 @@
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="0" t="n">
+      <c r="A134" s="2" t="n">
         <v>133</v>
       </c>
       <c r="B134" s="1" t="n">
@@ -9395,7 +9955,7 @@
       </c>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="0" t="n">
+      <c r="A135" s="2" t="n">
         <v>134</v>
       </c>
       <c r="B135" s="1" t="n">
@@ -9414,7 +9974,7 @@
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="0" t="n">
+      <c r="A136" s="2" t="n">
         <v>135</v>
       </c>
       <c r="B136" s="1" t="n">
@@ -9433,7 +9993,7 @@
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="0" t="n">
+      <c r="A137" s="2" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="1" t="n">
@@ -9452,7 +10012,7 @@
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="0" t="n">
+      <c r="A138" s="2" t="n">
         <v>137</v>
       </c>
       <c r="B138" s="1" t="n">
@@ -9471,7 +10031,7 @@
       </c>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="0" t="n">
+      <c r="A139" s="2" t="n">
         <v>138</v>
       </c>
       <c r="B139" s="1" t="n">
@@ -9490,7 +10050,7 @@
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="0" t="n">
+      <c r="A140" s="2" t="n">
         <v>139</v>
       </c>
       <c r="B140" s="1" t="n">
@@ -9509,7 +10069,7 @@
       </c>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="0" t="n">
+      <c r="A141" s="2" t="n">
         <v>140</v>
       </c>
       <c r="B141" s="1" t="n">
@@ -9528,7 +10088,7 @@
       </c>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="0" t="n">
+      <c r="A142" s="2" t="n">
         <v>141</v>
       </c>
       <c r="B142" s="1" t="n">
@@ -9547,7 +10107,7 @@
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="0" t="n">
+      <c r="A143" s="2" t="n">
         <v>142</v>
       </c>
       <c r="B143" s="1" t="n">
@@ -9566,7 +10126,7 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="0" t="n">
+      <c r="A144" s="2" t="n">
         <v>143</v>
       </c>
       <c r="B144" s="1" t="n">
@@ -9585,7 +10145,7 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="0" t="n">
+      <c r="A145" s="2" t="n">
         <v>144</v>
       </c>
       <c r="B145" s="1" t="n">
@@ -9604,7 +10164,7 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="0" t="n">
+      <c r="A146" s="2" t="n">
         <v>145</v>
       </c>
       <c r="B146" s="1" t="n">
@@ -9623,7 +10183,7 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="0" t="n">
+      <c r="A147" s="2" t="n">
         <v>146</v>
       </c>
       <c r="B147" s="1" t="n">
@@ -9642,7 +10202,7 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="0" t="n">
+      <c r="A148" s="2" t="n">
         <v>147</v>
       </c>
       <c r="B148" s="1" t="n">
@@ -9661,7 +10221,7 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="0" t="n">
+      <c r="A149" s="2" t="n">
         <v>148</v>
       </c>
       <c r="B149" s="1" t="n">
@@ -9680,7 +10240,7 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="0" t="n">
+      <c r="A150" s="2" t="n">
         <v>149</v>
       </c>
       <c r="B150" s="1" t="n">
@@ -9699,7 +10259,7 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="0" t="n">
+      <c r="A151" s="2" t="n">
         <v>150</v>
       </c>
       <c r="B151" s="1" t="n">
@@ -9718,7 +10278,7 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="0" t="n">
+      <c r="A152" s="2" t="n">
         <v>151</v>
       </c>
       <c r="B152" s="1" t="n">
@@ -9737,7 +10297,7 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="0" t="n">
+      <c r="A153" s="2" t="n">
         <v>152</v>
       </c>
       <c r="B153" s="1" t="n">
@@ -9756,7 +10316,7 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="0" t="n">
+      <c r="A154" s="2" t="n">
         <v>153</v>
       </c>
       <c r="B154" s="1" t="n">
@@ -9775,7 +10335,7 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="0" t="n">
+      <c r="A155" s="2" t="n">
         <v>154</v>
       </c>
       <c r="B155" s="1" t="n">
@@ -9794,7 +10354,7 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="0" t="n">
+      <c r="A156" s="2" t="n">
         <v>155</v>
       </c>
       <c r="B156" s="1" t="n">
@@ -9813,7 +10373,7 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="0" t="n">
+      <c r="A157" s="2" t="n">
         <v>156</v>
       </c>
       <c r="B157" s="1" t="n">
@@ -9832,7 +10392,7 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="0" t="n">
+      <c r="A158" s="2" t="n">
         <v>157</v>
       </c>
       <c r="B158" s="1" t="n">
@@ -9851,7 +10411,7 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="0" t="n">
+      <c r="A159" s="2" t="n">
         <v>158</v>
       </c>
       <c r="B159" s="1" t="n">
@@ -9870,7 +10430,7 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="0" t="n">
+      <c r="A160" s="2" t="n">
         <v>159</v>
       </c>
       <c r="B160" s="1" t="n">
@@ -9889,7 +10449,7 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="0" t="n">
+      <c r="A161" s="2" t="n">
         <v>160</v>
       </c>
       <c r="B161" s="1" t="n">
@@ -9908,7 +10468,7 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="0" t="n">
+      <c r="A162" s="2" t="n">
         <v>161</v>
       </c>
       <c r="B162" s="1" t="n">
@@ -9927,7 +10487,7 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="0" t="n">
+      <c r="A163" s="2" t="n">
         <v>162</v>
       </c>
       <c r="B163" s="1" t="n">
@@ -9946,7 +10506,7 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="0" t="n">
+      <c r="A164" s="2" t="n">
         <v>163</v>
       </c>
       <c r="B164" s="1" t="n">
@@ -9965,7 +10525,7 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="0" t="n">
+      <c r="A165" s="2" t="n">
         <v>164</v>
       </c>
       <c r="B165" s="1" t="n">
@@ -9984,7 +10544,7 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="0" t="n">
+      <c r="A166" s="2" t="n">
         <v>165</v>
       </c>
       <c r="B166" s="1" t="n">
@@ -10003,7 +10563,7 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="0" t="n">
+      <c r="A167" s="2" t="n">
         <v>166</v>
       </c>
       <c r="B167" s="1" t="n">
@@ -10022,7 +10582,7 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="0" t="n">
+      <c r="A168" s="2" t="n">
         <v>167</v>
       </c>
       <c r="B168" s="1" t="n">
@@ -10041,7 +10601,7 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="0" t="n">
+      <c r="A169" s="2" t="n">
         <v>168</v>
       </c>
       <c r="B169" s="1" t="n">
@@ -10060,7 +10620,7 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="0" t="n">
+      <c r="A170" s="2" t="n">
         <v>169</v>
       </c>
       <c r="B170" s="1" t="n">
@@ -10079,7 +10639,7 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="0" t="n">
+      <c r="A171" s="2" t="n">
         <v>170</v>
       </c>
       <c r="B171" s="1" t="n">
@@ -10098,7 +10658,7 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="0" t="n">
+      <c r="A172" s="2" t="n">
         <v>171</v>
       </c>
       <c r="B172" s="1" t="n">
@@ -10117,7 +10677,7 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="0" t="n">
+      <c r="A173" s="2" t="n">
         <v>172</v>
       </c>
       <c r="B173" s="1" t="n">
@@ -10136,7 +10696,7 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="0" t="n">
+      <c r="A174" s="2" t="n">
         <v>173</v>
       </c>
       <c r="B174" s="1" t="n">
@@ -10155,7 +10715,7 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="0" t="n">
+      <c r="A175" s="2" t="n">
         <v>174</v>
       </c>
       <c r="B175" s="1" t="n">
@@ -10174,7 +10734,7 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="0" t="n">
+      <c r="A176" s="2" t="n">
         <v>175</v>
       </c>
       <c r="B176" s="1" t="n">
@@ -10193,7 +10753,7 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="0" t="n">
+      <c r="A177" s="2" t="n">
         <v>176</v>
       </c>
       <c r="B177" s="1" t="n">
@@ -10212,7 +10772,7 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="0" t="n">
+      <c r="A178" s="2" t="n">
         <v>177</v>
       </c>
       <c r="B178" s="1" t="n">
@@ -10231,7 +10791,7 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="0" t="n">
+      <c r="A179" s="2" t="n">
         <v>178</v>
       </c>
       <c r="B179" s="1" t="n">
@@ -10250,7 +10810,7 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="0" t="n">
+      <c r="A180" s="2" t="n">
         <v>179</v>
       </c>
       <c r="B180" s="1" t="n">
@@ -10269,7 +10829,7 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="0" t="n">
+      <c r="A181" s="2" t="n">
         <v>180</v>
       </c>
       <c r="B181" s="1" t="n">
@@ -10288,7 +10848,7 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="0" t="n">
+      <c r="A182" s="2" t="n">
         <v>181</v>
       </c>
       <c r="B182" s="1" t="n">
@@ -10307,7 +10867,7 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="0" t="n">
+      <c r="A183" s="2" t="n">
         <v>182</v>
       </c>
       <c r="B183" s="1" t="n">
@@ -10326,7 +10886,7 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="0" t="n">
+      <c r="A184" s="2" t="n">
         <v>183</v>
       </c>
       <c r="B184" s="1" t="n">
@@ -10345,7 +10905,7 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="0" t="n">
+      <c r="A185" s="2" t="n">
         <v>184</v>
       </c>
       <c r="B185" s="1" t="n">
@@ -10364,7 +10924,7 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="0" t="n">
+      <c r="A186" s="2" t="n">
         <v>185</v>
       </c>
       <c r="B186" s="1" t="n">
@@ -10383,7 +10943,7 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="0" t="n">
+      <c r="A187" s="2" t="n">
         <v>186</v>
       </c>
       <c r="B187" s="1" t="n">
@@ -10402,7 +10962,7 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="0" t="n">
+      <c r="A188" s="2" t="n">
         <v>187</v>
       </c>
       <c r="B188" s="1" t="n">
@@ -10421,7 +10981,7 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="0" t="n">
+      <c r="A189" s="2" t="n">
         <v>188</v>
       </c>
       <c r="B189" s="1" t="n">
@@ -10440,7 +11000,7 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="0" t="n">
+      <c r="A190" s="2" t="n">
         <v>189</v>
       </c>
       <c r="B190" s="1" t="n">
@@ -10459,7 +11019,7 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="0" t="n">
+      <c r="A191" s="2" t="n">
         <v>190</v>
       </c>
       <c r="B191" s="1" t="n">
@@ -10478,7 +11038,7 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="0" t="n">
+      <c r="A192" s="2" t="n">
         <v>191</v>
       </c>
       <c r="B192" s="1" t="n">
@@ -10497,7 +11057,7 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="0" t="n">
+      <c r="A193" s="2" t="n">
         <v>192</v>
       </c>
       <c r="B193" s="1" t="n">
@@ -10516,7 +11076,7 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="n">
+      <c r="A194" s="2" t="n">
         <v>193</v>
       </c>
       <c r="B194" s="1" t="n">
@@ -10535,7 +11095,7 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="n">
+      <c r="A195" s="2" t="n">
         <v>194</v>
       </c>
       <c r="B195" s="1" t="n">
@@ -10554,7 +11114,7 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0" t="n">
+      <c r="A196" s="2" t="n">
         <v>195</v>
       </c>
       <c r="B196" s="1" t="n">
@@ -10573,7 +11133,7 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0" t="n">
+      <c r="A197" s="2" t="n">
         <v>196</v>
       </c>
       <c r="B197" s="1" t="n">
@@ -10592,7 +11152,7 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0" t="n">
+      <c r="A198" s="2" t="n">
         <v>197</v>
       </c>
       <c r="B198" s="1" t="n">
@@ -10611,7 +11171,7 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="0" t="n">
+      <c r="A199" s="2" t="n">
         <v>198</v>
       </c>
       <c r="B199" s="1" t="n">
@@ -10630,7 +11190,7 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="0" t="n">
+      <c r="A200" s="2" t="n">
         <v>199</v>
       </c>
       <c r="B200" s="1" t="n">
@@ -10649,7 +11209,7 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="0" t="n">
+      <c r="A201" s="2" t="n">
         <v>200</v>
       </c>
       <c r="B201" s="1" t="n">
@@ -10684,7 +11244,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E69"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1"/>
@@ -11044,58 +11604,58 @@
       <c r="E51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="5"/>
+      <c r="C52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="5"/>
+      <c r="C53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="5"/>
+      <c r="C54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="5"/>
+      <c r="C55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="5"/>
+      <c r="C56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C57" s="5"/>
+      <c r="C57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C58" s="5"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C59" s="5"/>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C60" s="5"/>
+      <c r="C60" s="3"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C61" s="5"/>
+      <c r="C61" s="3"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="5"/>
+      <c r="C62" s="3"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C63" s="5"/>
+      <c r="C63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C64" s="5"/>
+      <c r="C64" s="3"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C65" s="5"/>
+      <c r="C65" s="3"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C66" s="5"/>
+      <c r="C66" s="3"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C67" s="5"/>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="5"/>
+      <c r="C68" s="3"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C69" s="5"/>
+      <c r="C69" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
